--- a/registration_forms/031_legal_collection_forum_registration--registration_forms.xlsx
+++ b/registration_forms/031_legal_collection_forum_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,8 +1087,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_terms_and_conditions'}</t>
+          <t>i_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the terms and conditions'}</t>
+          <t>I agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_payment_terms'}</t>
+          <t>i_agree_to_the_payment_terms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the payment terms'}</t>
+          <t>I agree to the payment terms</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'forum'}</t>
+          <t>forum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Forum'}</t>
+          <t>Forum</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'live'}</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Live'}</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'postponed'}</t>
+          <t>postponed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Postponed'}</t>
+          <t>Postponed</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
